--- a/Packages/cn.etetet.twstilemap/Luban/Config/Datas/TileItem.xlsx
+++ b/Packages/cn.etetet.twstilemap/Luban/Config/Datas/TileItem.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Id</t>
   </si>
   <si>
-    <t>LandType</t>
+    <t>Title</t>
   </si>
   <si>
     <t>Desc</t>
@@ -47,12 +47,18 @@
     <t>CellData</t>
   </si>
   <si>
-    <t>PrefabName</t>
+    <t>TileData</t>
+  </si>
+  <si>
+    <t>PreviewPrefabData</t>
   </si>
   <si>
     <t>UIName</t>
   </si>
   <si>
+    <t>GroupID</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -68,10 +74,13 @@
     <t>(list#sep=,),int</t>
   </si>
   <si>
+    <t>map,string,TileType</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
-    <t>类型</t>
+    <t>标题</t>
   </si>
   <si>
     <t>描述</t>
@@ -80,25 +89,181 @@
     <t>数值</t>
   </si>
   <si>
+    <t>地格数据(宽、高)</t>
+  </si>
+  <si>
     <t>地格数据</t>
   </si>
   <si>
-    <t>资源名称</t>
+    <t>预览资源名称</t>
   </si>
   <si>
     <t>UI资源名称</t>
   </si>
   <si>
+    <t>组ID</t>
+  </si>
+  <si>
+    <t>竖桥</t>
+  </si>
+  <si>
+    <t>桥，可竖向同行</t>
+  </si>
+  <si>
+    <t>价格_0</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>CustomRuleTile_Normal_Bridge_V</t>
+  </si>
+  <si>
+    <t>自定义规则地块</t>
+  </si>
+  <si>
+    <t>单个</t>
+  </si>
+  <si>
+    <t>Build_Bridge_0</t>
+  </si>
+  <si>
+    <t>横桥</t>
+  </si>
+  <si>
+    <t>桥，可横向同行</t>
+  </si>
+  <si>
+    <t>CustomRuleTile_Normal_Bridge_H</t>
+  </si>
+  <si>
+    <t>Build_Bridge_1</t>
+  </si>
+  <si>
     <t>农田</t>
   </si>
   <si>
-    <t>农田，可种植农作物</t>
-  </si>
-  <si>
-    <t>价格_0</t>
+    <t>农田，无农作物</t>
   </si>
   <si>
     <t>1,1</t>
+  </si>
+  <si>
+    <t>Floor_Farm_1</t>
+  </si>
+  <si>
+    <t>地块</t>
+  </si>
+  <si>
+    <t>拖拽</t>
+  </si>
+  <si>
+    <t>Build_Farm_0</t>
+  </si>
+  <si>
+    <t>栅栏</t>
+  </si>
+  <si>
+    <t>CustomRuleTile_Ring_Fence</t>
+  </si>
+  <si>
+    <t>Build_Fence</t>
+  </si>
+  <si>
+    <t>小火</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>FDR_Grasslands_716</t>
+  </si>
+  <si>
+    <t>精灵</t>
+  </si>
+  <si>
+    <t>Build_Fire_0</t>
+  </si>
+  <si>
+    <t>大火</t>
+  </si>
+  <si>
+    <t>FDR_Grasslands_734</t>
+  </si>
+  <si>
+    <t>Build_Fire_1</t>
+  </si>
+  <si>
+    <t>路标</t>
+  </si>
+  <si>
+    <t>FDR_Grasslands_363</t>
+  </si>
+  <si>
+    <t>Build_Signage_0</t>
+  </si>
+  <si>
+    <t>路标，向左</t>
+  </si>
+  <si>
+    <t>FDR_Grasslands_389</t>
+  </si>
+  <si>
+    <t>Build_Signage_Left</t>
+  </si>
+  <si>
+    <t>路标，向右</t>
+  </si>
+  <si>
+    <t>FDR_Grasslands_388</t>
+  </si>
+  <si>
+    <t>Build_Signage_Right</t>
+  </si>
+  <si>
+    <t>桌子</t>
+  </si>
+  <si>
+    <t>大桌子</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>CustomRuleTile_Normal_BigTable</t>
+  </si>
+  <si>
+    <t>Build_Table_0</t>
+  </si>
+  <si>
+    <t>小桌子</t>
+  </si>
+  <si>
+    <t>FDR_Grasslands_366</t>
+  </si>
+  <si>
+    <t>Build_Table_1</t>
+  </si>
+  <si>
+    <t>长桌子</t>
+  </si>
+  <si>
+    <t>CustomRuleTile_Normal_LitTable</t>
+  </si>
+  <si>
+    <t>Build_Table_2</t>
+  </si>
+  <si>
+    <t>树</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>CustomRuleTile_Normal_Tree</t>
+  </si>
+  <si>
+    <t>Build_Tree</t>
   </si>
 </sst>
 </file>
@@ -725,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -734,6 +899,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1058,19 +1226,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
     <col min="2" max="3" width="15.875" style="2" customWidth="1"/>
     <col min="4" max="4" width="25" style="2" customWidth="1"/>
     <col min="5" max="7" width="31.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26" style="2" customWidth="1"/>
-    <col min="9" max="9" width="25.375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="46.125" style="3" customWidth="1"/>
+    <col min="9" max="10" width="26" style="3" customWidth="1"/>
+    <col min="11" max="12" width="26" style="2" customWidth="1"/>
+    <col min="13" max="13" width="25.375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1089,174 +1260,555 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:9">
+    <row r="2" s="1" customFormat="1" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="2:7">
+    <row r="4" s="2" customFormat="1" spans="2:14">
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="5">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" spans="2:7">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+    <row r="5" s="2" customFormat="1" spans="2:14">
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="5">
+        <v>10</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="2:7">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+    <row r="6" s="2" customFormat="1" spans="2:14">
+      <c r="B6" s="3">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="5">
+        <v>5</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="2">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="2:7">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+    <row r="7" s="2" customFormat="1" spans="2:14">
+      <c r="B7" s="3">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="5">
+        <v>10</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="2:7">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+    <row r="8" s="2" customFormat="1" spans="2:14">
+      <c r="B8" s="3">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="5">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="2:7">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+    <row r="9" s="2" customFormat="1" spans="2:14">
+      <c r="B9" s="3">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="5">
+        <v>10</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="2:7">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+    <row r="10" spans="2:14">
+      <c r="B10" s="3">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="5">
+        <v>10</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" s="2" customFormat="1" spans="2:7">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+    <row r="11" spans="2:14">
+      <c r="B11" s="3">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="5">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="12" spans="5:7">
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+    <row r="12" spans="2:14">
+      <c r="B12" s="3">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="5">
+        <v>10</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N12" s="2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="5:5">
-      <c r="E13" s="4"/>
+    <row r="13" spans="2:14">
+      <c r="B13" s="3">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="5">
+        <v>10</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N13" s="2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="14" spans="5:7">
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
+    <row r="14" spans="2:14">
+      <c r="B14" s="3">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="5">
+        <v>10</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N14" s="2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="5:7">
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
+    <row r="15" spans="2:14">
+      <c r="B15" s="3">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N15" s="2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="5:7">
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="5:7">
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
+    <row r="16" spans="2:14">
+      <c r="B16" s="3">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="5">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N16" s="2">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="9">
     <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:L2"/>
     <mergeCell ref="E3:F3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Packages/cn.etetet.twstilemap/Luban/Config/Datas/TileItem.xlsx
+++ b/Packages/cn.etetet.twstilemap/Luban/Config/Datas/TileItem.xlsx
@@ -1237,7 +1237,7 @@
     <col min="9" max="10" width="26" style="3" customWidth="1"/>
     <col min="11" max="12" width="26" style="2" customWidth="1"/>
     <col min="13" max="13" width="25.375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="12" style="2" customWidth="1"/>
+    <col min="14" max="14" width="37.125" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
